--- a/src/main/resources/recipeDataExl/recipeData.xlsx
+++ b/src/main/resources/recipeDataExl/recipeData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ljp1\IdeaProjects\monthlySum\src\main\resources\recipeDataExl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6A44B5-B7AA-4D28-B338-37CC0B9613BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC30AF6C-6288-4AD4-AEA2-91C4D4ACAFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="146">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -550,12 +550,32 @@
   <si>
     <t>白胡椒粉</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腌渍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20分钟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试菜</t>
+  </si>
+  <si>
+    <t>测试原料1</t>
+  </si>
+  <si>
+    <t>侧手iambic</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
+  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -601,12 +621,18 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -621,15 +647,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -910,19 +942,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1669B0E-7190-4D05-AAA2-55A44F80980F}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.6640625" style="8" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -930,7 +965,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -938,7 +973,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -946,7 +981,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="8">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -954,7 +989,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="8">
         <v>5</v>
       </c>
       <c r="B6" t="s">
@@ -962,7 +997,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="8">
         <v>6</v>
       </c>
       <c r="B7" t="s">
@@ -970,7 +1005,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="A8" s="8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
@@ -978,7 +1013,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="8">
         <v>8</v>
       </c>
       <c r="B9" t="s">
@@ -986,7 +1021,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="8">
         <v>9</v>
       </c>
       <c r="B10" t="s">
@@ -994,7 +1029,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="8">
         <v>10</v>
       </c>
       <c r="B11" t="s">
@@ -1002,7 +1037,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
+      <c r="A12" s="8">
         <v>11</v>
       </c>
       <c r="B12" t="s">
@@ -1010,7 +1045,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13">
+      <c r="A13" s="8">
         <v>12</v>
       </c>
       <c r="B13" t="s">
@@ -1018,7 +1053,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14">
+      <c r="A14" s="8">
         <v>13</v>
       </c>
       <c r="B14" t="s">
@@ -1026,7 +1061,7 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15">
+      <c r="A15" s="8">
         <v>14</v>
       </c>
       <c r="B15" t="s">
@@ -1034,7 +1069,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16">
+      <c r="A16" s="8">
         <v>15</v>
       </c>
       <c r="B16" t="s">
@@ -1042,7 +1077,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
+      <c r="A17" s="8">
         <v>16</v>
       </c>
       <c r="B17" t="s">
@@ -1050,7 +1085,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
+      <c r="A18" s="8">
         <v>17</v>
       </c>
       <c r="B18" t="s">
@@ -1058,7 +1093,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
+      <c r="A19" s="8">
         <v>18</v>
       </c>
       <c r="B19" t="s">
@@ -1066,7 +1101,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="A20" s="8">
         <v>19</v>
       </c>
       <c r="B20" t="s">
@@ -1074,7 +1109,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="A21" s="8">
         <v>20</v>
       </c>
       <c r="B21" t="s">
@@ -1082,7 +1117,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22">
+      <c r="A22" s="8">
         <v>21</v>
       </c>
       <c r="B22" t="s">
@@ -1090,7 +1125,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23">
+      <c r="A23" s="8">
         <v>22</v>
       </c>
       <c r="B23" t="s">
@@ -1098,7 +1133,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24">
+      <c r="A24" s="8">
         <v>23</v>
       </c>
       <c r="B24" t="s">
@@ -1106,11 +1141,19 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25">
+      <c r="A25" s="8">
         <v>24</v>
       </c>
       <c r="B25" t="s">
         <v>127</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>241006212047</v>
+      </c>
+      <c r="B26" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1121,19 +1164,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" style="8" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -1141,7 +1187,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -1149,7 +1195,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -1157,7 +1203,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="8">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -1165,7 +1211,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="8">
         <v>5</v>
       </c>
       <c r="B6" t="s">
@@ -1173,7 +1219,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="8">
         <v>6</v>
       </c>
       <c r="B7" t="s">
@@ -1181,7 +1227,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="A8" s="8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
@@ -1189,7 +1235,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="8">
         <v>8</v>
       </c>
       <c r="B9" t="s">
@@ -1197,7 +1243,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="8">
         <v>9</v>
       </c>
       <c r="B10" t="s">
@@ -1205,7 +1251,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="8">
         <v>10</v>
       </c>
       <c r="B11" t="s">
@@ -1213,7 +1259,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
+      <c r="A12" s="8">
         <v>11</v>
       </c>
       <c r="B12" t="s">
@@ -1221,7 +1267,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13">
+      <c r="A13" s="8">
         <v>12</v>
       </c>
       <c r="B13" t="s">
@@ -1229,7 +1275,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14">
+      <c r="A14" s="8">
         <v>13</v>
       </c>
       <c r="B14" t="s">
@@ -1237,7 +1283,7 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15">
+      <c r="A15" s="8">
         <v>14</v>
       </c>
       <c r="B15" t="s">
@@ -1245,7 +1291,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16">
+      <c r="A16" s="8">
         <v>15</v>
       </c>
       <c r="B16" t="s">
@@ -1253,7 +1299,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
+      <c r="A17" s="8">
         <v>16</v>
       </c>
       <c r="B17" t="s">
@@ -1261,7 +1307,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
+      <c r="A18" s="8">
         <v>17</v>
       </c>
       <c r="B18" t="s">
@@ -1269,7 +1315,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
+      <c r="A19" s="8">
         <v>18</v>
       </c>
       <c r="B19" t="s">
@@ -1277,7 +1323,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="A20" s="8">
         <v>19</v>
       </c>
       <c r="B20" t="s">
@@ -1285,7 +1331,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="A21" s="8">
         <v>20</v>
       </c>
       <c r="B21" t="s">
@@ -1293,7 +1339,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22">
+      <c r="A22" s="8">
         <v>21</v>
       </c>
       <c r="B22" t="s">
@@ -1301,7 +1347,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23">
+      <c r="A23" s="8">
         <v>22</v>
       </c>
       <c r="B23" t="s">
@@ -1309,7 +1355,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24">
+      <c r="A24" s="8">
         <v>23</v>
       </c>
       <c r="B24" t="s">
@@ -1317,7 +1363,7 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25">
+      <c r="A25" s="8">
         <v>24</v>
       </c>
       <c r="B25" t="s">
@@ -1325,7 +1371,7 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26">
+      <c r="A26" s="8">
         <v>25</v>
       </c>
       <c r="B26" t="s">
@@ -1333,7 +1379,7 @@
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27">
+      <c r="A27" s="8">
         <v>26</v>
       </c>
       <c r="B27" t="s">
@@ -1341,7 +1387,7 @@
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28">
+      <c r="A28" s="8">
         <v>27</v>
       </c>
       <c r="B28" t="s">
@@ -1349,7 +1395,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29">
+      <c r="A29" s="8">
         <v>28</v>
       </c>
       <c r="B29" t="s">
@@ -1357,7 +1403,7 @@
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30">
+      <c r="A30" s="8">
         <v>29</v>
       </c>
       <c r="B30" t="s">
@@ -1365,7 +1411,7 @@
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31">
+      <c r="A31" s="8">
         <v>30</v>
       </c>
       <c r="B31" t="s">
@@ -1373,7 +1419,7 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32">
+      <c r="A32" s="8">
         <v>31</v>
       </c>
       <c r="B32" t="s">
@@ -1381,7 +1427,7 @@
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33">
+      <c r="A33" s="8">
         <v>32</v>
       </c>
       <c r="B33" t="s">
@@ -1389,7 +1435,7 @@
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34">
+      <c r="A34" s="8">
         <v>33</v>
       </c>
       <c r="B34" t="s">
@@ -1397,7 +1443,7 @@
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35">
+      <c r="A35" s="8">
         <v>34</v>
       </c>
       <c r="B35" t="s">
@@ -1405,7 +1451,7 @@
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36">
+      <c r="A36" s="8">
         <v>35</v>
       </c>
       <c r="B36" t="s">
@@ -1413,7 +1459,7 @@
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37">
+      <c r="A37" s="8">
         <v>36</v>
       </c>
       <c r="B37" t="s">
@@ -1421,7 +1467,7 @@
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38">
+      <c r="A38" s="8">
         <v>37</v>
       </c>
       <c r="B38" t="s">
@@ -1429,7 +1475,7 @@
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39">
+      <c r="A39" s="8">
         <v>38</v>
       </c>
       <c r="B39" t="s">
@@ -1437,7 +1483,7 @@
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40">
+      <c r="A40" s="8">
         <v>39</v>
       </c>
       <c r="B40" t="s">
@@ -1445,7 +1491,7 @@
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41">
+      <c r="A41" s="8">
         <v>40</v>
       </c>
       <c r="B41" t="s">
@@ -1453,7 +1499,7 @@
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42">
+      <c r="A42" s="8">
         <v>41</v>
       </c>
       <c r="B42" t="s">
@@ -1461,7 +1507,7 @@
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43">
+      <c r="A43" s="8">
         <v>42</v>
       </c>
       <c r="B43" t="s">
@@ -1469,7 +1515,7 @@
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44">
+      <c r="A44" s="8">
         <v>43</v>
       </c>
       <c r="B44" t="s">
@@ -1477,7 +1523,7 @@
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45">
+      <c r="A45" s="8">
         <v>44</v>
       </c>
       <c r="B45" t="s">
@@ -1485,7 +1531,7 @@
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46">
+      <c r="A46" s="8">
         <v>45</v>
       </c>
       <c r="B46" t="s">
@@ -1493,7 +1539,7 @@
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47">
+      <c r="A47" s="8">
         <v>46</v>
       </c>
       <c r="B47" t="s">
@@ -1501,7 +1547,7 @@
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48">
+      <c r="A48" s="8">
         <v>47</v>
       </c>
       <c r="B48" t="s">
@@ -1509,7 +1555,7 @@
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49">
+      <c r="A49" s="8">
         <v>48</v>
       </c>
       <c r="B49" t="s">
@@ -1517,7 +1563,7 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50">
+      <c r="A50" s="8">
         <v>49</v>
       </c>
       <c r="B50" t="s">
@@ -1525,7 +1571,7 @@
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51">
+      <c r="A51" s="8">
         <v>50</v>
       </c>
       <c r="B51" t="s">
@@ -1533,7 +1579,7 @@
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52">
+      <c r="A52" s="8">
         <v>51</v>
       </c>
       <c r="B52" t="s">
@@ -1541,11 +1587,35 @@
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53">
+      <c r="A53" s="8">
         <v>52</v>
       </c>
       <c r="B53" t="s">
         <v>139</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="8">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="10">
+        <v>24100621204701</v>
+      </c>
+      <c r="B55" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="8">
+        <v>24100621204702</v>
+      </c>
+      <c r="B56" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1556,2344 +1626,2444 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06AE1D6D-B3AE-4A50-959B-F8CD43727203}">
-  <dimension ref="A1:F126"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11">
+        <v>1</v>
+      </c>
+      <c r="C2" s="11">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
+      <c r="B3" s="11">
+        <v>1</v>
+      </c>
+      <c r="C3" s="11">
         <v>2</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
+      <c r="A4" s="11">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
+      <c r="B4" s="11">
+        <v>1</v>
+      </c>
+      <c r="C4" s="11">
         <v>3</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>0.25</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="11">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
+      <c r="B5" s="11">
+        <v>1</v>
+      </c>
+      <c r="C5" s="11">
         <v>4</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>120</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="11">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="11">
         <v>2</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="11">
         <v>4</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>80</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7">
+      <c r="A7" s="11">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="11">
         <v>2</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="11">
         <v>5</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8">
+      <c r="A8" s="11">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="11">
         <v>2</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="11">
         <v>6</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>0.3</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="11">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="11">
         <v>3</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="11">
         <v>4</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>80</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10">
+      <c r="A10" s="11">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="11">
         <v>3</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="11">
         <v>5</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11">
+      <c r="A11" s="11">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="11">
         <v>3</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="11">
         <v>6</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>0.3</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12">
+      <c r="A12" s="11">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="11">
         <v>4</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="11">
         <v>7</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="3">
         <v>150</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13">
+      <c r="A13" s="11">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="11">
         <v>4</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="11">
         <v>2</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>6</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14">
+      <c r="A14" s="11">
         <v>13</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="11">
         <v>4</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="11">
         <v>8</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="3">
         <v>150</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15">
+      <c r="A15" s="11">
         <v>14</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="11">
         <v>4</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="11">
         <v>9</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16">
+      <c r="A16" s="11">
         <v>15</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="11">
         <v>5</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="11">
         <v>10</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="3">
         <v>0.5</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17">
+      <c r="A17" s="11">
         <v>16</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="11">
         <v>5</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="11">
         <v>11</v>
       </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18">
+      <c r="A18" s="11">
         <v>17</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="11">
         <v>6</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="11">
         <v>12</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="3">
         <v>250</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19">
+      <c r="A19" s="11">
         <v>18</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="11">
         <v>6</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="11">
         <v>13</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="3">
         <v>0.5</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="A20" s="11">
         <v>19</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="11">
         <v>6</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="11">
         <v>9</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
         <v>2</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21">
+      <c r="A21" s="11">
         <v>20</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="11">
         <v>6</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="11">
         <v>14</v>
       </c>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22">
+      <c r="A22" s="11">
         <v>21</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="11">
         <v>6</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="11">
         <v>15</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="3">
         <v>0.5</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23">
+      <c r="A23" s="11">
         <v>22</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="11">
         <v>6</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="11">
         <v>2</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="2">
         <v>2</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24">
+      <c r="A24" s="11">
         <v>23</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="11">
         <v>7</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="11">
         <v>12</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="3">
         <v>250</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25">
+      <c r="A25" s="11">
         <v>24</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="11">
         <v>7</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="11">
         <v>15</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="3">
         <v>0.5</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26">
+      <c r="A26" s="11">
         <v>25</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="11">
         <v>7</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="11">
         <v>2</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="2">
         <v>2</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27">
+      <c r="A27" s="11">
         <v>26</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="11">
         <v>7</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="11">
         <v>3</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="2">
         <v>0.25</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28">
+      <c r="A28" s="11">
         <v>27</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="11">
         <v>7</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="11">
         <v>13</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" s="3">
         <v>0.5</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29">
+      <c r="A29" s="11">
         <v>28</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="11">
         <v>7</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="11">
         <v>16</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="2">
         <v>3</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30">
+      <c r="A30" s="11">
         <v>29</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="11">
         <v>7</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="11">
         <v>9</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="2">
         <v>2</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31">
+      <c r="A31" s="11">
         <v>30</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="11">
         <v>7</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="11">
         <v>14</v>
       </c>
-      <c r="D31" s="1">
-        <v>1</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="D31" s="3">
+        <v>1</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32">
+      <c r="A32" s="11">
         <v>31</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="11">
         <v>8</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="11">
         <v>12</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33">
+      <c r="A33" s="11">
         <v>32</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="11">
         <v>8</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="11">
         <v>2</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="2">
         <v>2</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34">
+      <c r="A34" s="11">
         <v>33</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="11">
         <v>8</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="11">
         <v>17</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="2">
         <v>0.25</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35">
+      <c r="A35" s="11">
         <v>34</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="11">
         <v>8</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="11">
         <v>6</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D35" s="3">
         <v>0.5</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36">
+      <c r="A36" s="11">
         <v>35</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="11">
         <v>9</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="11">
         <v>12</v>
       </c>
-      <c r="D36" s="1">
+      <c r="D36" s="3">
         <v>200</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37">
+      <c r="A37" s="11">
         <v>36</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="11">
         <v>9</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="11">
         <v>18</v>
       </c>
-      <c r="D37" s="1">
-        <v>1</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="D37" s="3">
+        <v>1</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38">
+      <c r="A38" s="11">
         <v>37</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="11">
         <v>9</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="11">
         <v>19</v>
       </c>
-      <c r="D38" s="1">
-        <v>1</v>
-      </c>
-      <c r="E38" s="1" t="s">
+      <c r="D38" s="3">
+        <v>1</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39">
+      <c r="A39" s="11">
         <v>38</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="11">
         <v>9</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="11">
         <v>9</v>
       </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="D39" s="2">
+        <v>1</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40">
+      <c r="A40" s="11">
         <v>39</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="11">
         <v>10</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="11">
         <v>12</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D40" s="3">
         <v>100</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41">
+      <c r="A41" s="11">
         <v>40</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="11">
         <v>10</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="11">
         <v>20</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D41" s="3">
         <v>250</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42">
+      <c r="A42" s="11">
         <v>41</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="11">
         <v>10</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="11">
         <v>3</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D42" s="3">
         <v>0.16</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43">
+      <c r="A43" s="11">
         <v>42</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="11">
         <v>10</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="11">
         <v>16</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="2">
         <v>3</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44">
+      <c r="A44" s="11">
         <v>43</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="11">
         <v>10</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="11">
         <v>21</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D44" s="3">
         <v>50</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45">
+      <c r="A45" s="11">
         <v>44</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="11">
         <v>10</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="11">
         <v>22</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D45" s="3">
         <v>6</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46">
+      <c r="A46" s="11">
         <v>45</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="11">
         <v>11</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="11">
         <v>22</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D46" s="3">
         <v>250</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="6" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47">
+      <c r="A47" s="11">
         <v>46</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="11">
         <v>11</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="11">
         <v>6</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="2">
         <v>0.3</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48">
+      <c r="A48" s="11">
         <v>47</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="11">
         <v>11</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="11">
         <v>9</v>
       </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="D48" s="2">
+        <v>1</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49">
+      <c r="A49" s="11">
         <v>48</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="11">
         <v>12</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="11">
         <v>12</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49" s="3">
         <v>250</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50">
+      <c r="A50" s="11">
         <v>49</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="11">
         <v>12</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="11">
         <v>17</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D50" s="3">
         <v>0.16</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="3" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51">
+      <c r="A51" s="11">
         <v>50</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="11">
         <v>12</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="11">
         <v>6</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D51" s="3">
         <v>0.5</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52">
+      <c r="A52" s="11">
         <v>51</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="11">
         <v>13</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="11">
         <v>12</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D52" s="3">
         <v>250</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53">
+      <c r="A53" s="11">
         <v>52</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="11">
         <v>13</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="11">
         <v>2</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D53" s="3">
         <v>3</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="3" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54">
+      <c r="A54" s="11">
         <v>53</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="11">
         <v>13</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="11">
         <v>6</v>
       </c>
-      <c r="D54" s="1">
-        <v>1</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="D54" s="3">
+        <v>1</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55">
+      <c r="A55" s="11">
         <v>54</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="11">
         <v>14</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="11">
         <v>20</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D55" s="3">
         <v>0.125</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56">
+      <c r="A56" s="11">
         <v>55</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="11">
         <v>14</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="11">
         <v>10</v>
       </c>
-      <c r="D56" s="1">
+      <c r="D56" s="3">
         <v>150</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57">
+      <c r="A57" s="11">
         <v>56</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="11">
         <v>14</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="11">
         <v>23</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D57" s="3">
         <v>0.5</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58">
+      <c r="A58" s="11">
         <v>57</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="11">
         <v>14</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="11">
         <v>24</v>
       </c>
-      <c r="D58" s="1">
-        <v>1</v>
-      </c>
-      <c r="E58" s="1" t="s">
+      <c r="D58" s="3">
+        <v>1</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59">
+      <c r="A59" s="11">
         <v>58</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="11">
         <v>15</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="11">
         <v>4</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D59" s="3">
         <v>120</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60">
+      <c r="A60" s="11">
         <v>59</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="11">
         <v>15</v>
       </c>
-      <c r="C60">
-        <v>1</v>
-      </c>
-      <c r="D60" s="1">
+      <c r="C60" s="11">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3">
         <v>5</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F60" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61">
+      <c r="A61" s="11">
         <v>60</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="11">
         <v>15</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="11">
         <v>2</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="2">
         <v>2</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62">
+      <c r="A62" s="11">
         <v>61</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="11">
         <v>15</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="11">
         <v>3</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="2">
         <v>0.25</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63">
+      <c r="A63" s="11">
         <v>62</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="11">
         <v>15</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="11">
         <v>6</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="2">
         <v>0.3</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64">
+      <c r="A64" s="11">
         <v>63</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="11">
         <v>16</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="11">
         <v>12</v>
       </c>
-      <c r="D64" s="1">
+      <c r="D64" s="3">
         <v>100</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65">
+      <c r="A65" s="11">
         <v>64</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="11">
         <v>16</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="11">
         <v>22</v>
       </c>
-      <c r="D65" s="1">
+      <c r="D65" s="3">
         <v>12</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E65" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F65" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66">
+      <c r="A66" s="11">
         <v>65</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="11">
         <v>16</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="11">
         <v>25</v>
       </c>
-      <c r="D66">
-        <v>1</v>
-      </c>
-      <c r="E66" s="1" t="s">
+      <c r="D66" s="2">
+        <v>1</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F66" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67">
+      <c r="A67" s="11">
         <v>66</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="11">
         <v>16</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="11">
         <v>3</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="2">
         <v>0.16</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" s="3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68">
+      <c r="A68" s="11">
         <v>67</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="11">
         <v>16</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="11">
         <v>16</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="2">
         <v>3</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E68" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F68" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69">
+      <c r="A69" s="11">
         <v>68</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="11">
         <v>17</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="11">
         <v>12</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="2">
         <v>3</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="F69" s="3" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70">
+      <c r="A70" s="11">
         <v>69</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="11">
         <v>17</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="11">
         <v>25</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="2">
         <v>3</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E70" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F70" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71">
+      <c r="A71" s="11">
         <v>70</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="11">
         <v>17</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="11">
         <v>16</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="2">
         <v>3</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="F71" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72">
+      <c r="A72" s="11">
         <v>71</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="11">
         <v>18</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="11">
         <v>10</v>
       </c>
-      <c r="D72">
-        <v>1</v>
-      </c>
-      <c r="E72" t="s">
+      <c r="D72" s="2">
+        <v>1</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="F72" s="3" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73">
+      <c r="A73" s="11">
         <v>72</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="11">
         <v>18</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="11">
         <v>2</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="2">
         <v>2</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E73" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="F73" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74">
+      <c r="A74" s="11">
         <v>73</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="11">
         <v>18</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="11">
         <v>15</v>
       </c>
-      <c r="D74" s="1">
+      <c r="D74" s="3">
         <v>0.5</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F74" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75">
+      <c r="A75" s="11">
         <v>74</v>
       </c>
-      <c r="B75">
+      <c r="B75" s="11">
         <v>18</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="11">
         <v>9</v>
       </c>
-      <c r="D75" s="1">
-        <v>1</v>
-      </c>
-      <c r="E75" s="5" t="s">
+      <c r="D75" s="3">
+        <v>1</v>
+      </c>
+      <c r="E75" s="7" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="16" x14ac:dyDescent="0.3">
-      <c r="A76">
+      <c r="A76" s="11">
         <v>75</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="11">
         <v>19</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="11">
         <v>4</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="2">
         <v>100</v>
       </c>
-      <c r="E76" s="5" t="s">
+      <c r="E76" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77">
+      <c r="A77" s="11">
         <v>76</v>
       </c>
-      <c r="B77">
+      <c r="B77" s="11">
         <v>19</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="11">
         <v>5</v>
       </c>
-      <c r="D77">
-        <v>1</v>
-      </c>
-      <c r="E77" t="s">
+      <c r="D77" s="2">
+        <v>1</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="F77" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="16.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78">
+      <c r="A78" s="11">
         <v>77</v>
       </c>
-      <c r="B78">
+      <c r="B78" s="11">
         <v>19</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="11">
         <v>6</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="2">
         <v>0.3</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E78" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="F78" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79">
+      <c r="A79" s="11">
         <v>78</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="11">
         <v>20</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="11">
         <v>26</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E79" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80">
+      <c r="A80" s="11">
         <v>79</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="11">
         <v>20</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="11">
         <v>27</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E80" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81">
+      <c r="A81" s="11">
         <v>80</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="11">
         <v>20</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="11">
         <v>28</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E81" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82">
+      <c r="A82" s="11">
         <v>81</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="11">
         <v>20</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="11">
         <v>29</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83">
+      <c r="A83" s="11">
         <v>82</v>
       </c>
-      <c r="B83">
+      <c r="B83" s="11">
         <v>20</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="11">
         <v>30</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E83" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84">
+      <c r="A84" s="11">
         <v>83</v>
       </c>
-      <c r="B84">
+      <c r="B84" s="11">
         <v>20</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="11">
         <v>31</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E84" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F84" t="s">
+      <c r="F84" s="2" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85">
+      <c r="A85" s="11">
         <v>84</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="11">
         <v>20</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="11">
         <v>32</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E85" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86">
+      <c r="A86" s="11">
         <v>85</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="11">
         <v>20</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="11">
         <v>33</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87">
+      <c r="A87" s="11">
         <v>86</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="11">
         <v>20</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="11">
         <v>14</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E87" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88">
+      <c r="A88" s="11">
         <v>87</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="11">
         <v>20</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="11">
         <v>34</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E88" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89">
+      <c r="A89" s="11">
         <v>88</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="11">
         <v>20</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="11">
         <v>35</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E89" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F89" t="s">
+      <c r="F89" s="2" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90">
+      <c r="A90" s="11">
         <v>89</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="11">
         <v>21</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="11">
         <v>37</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="2">
         <v>3</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E90" s="2" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91">
+      <c r="A91" s="11">
         <v>90</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="11">
         <v>21</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="11">
         <v>6</v>
       </c>
-      <c r="D91">
-        <v>1</v>
-      </c>
-      <c r="E91" t="s">
+      <c r="D91" s="2">
+        <v>1</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92">
+      <c r="A92" s="11">
         <v>91</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="11">
         <v>21</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="11">
         <v>28</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="2">
         <v>2</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E92" s="2" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93">
+      <c r="A93" s="11">
         <v>92</v>
       </c>
-      <c r="B93">
+      <c r="B93" s="11">
         <v>21</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="11">
         <v>38</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E93" t="s">
+      <c r="E93" s="2" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94">
+      <c r="A94" s="11">
         <v>93</v>
       </c>
-      <c r="B94">
+      <c r="B94" s="11">
         <v>21</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="11">
         <v>34</v>
       </c>
-      <c r="D94">
-        <v>1</v>
-      </c>
-      <c r="E94" t="s">
+      <c r="D94" s="2">
+        <v>1</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95">
+      <c r="A95" s="11">
         <v>94</v>
       </c>
-      <c r="B95">
+      <c r="B95" s="11">
         <v>21</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="11">
         <v>39</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="2">
         <v>2</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E95" s="2" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96">
+      <c r="A96" s="11">
         <v>95</v>
       </c>
-      <c r="B96">
+      <c r="B96" s="11">
         <v>21</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="11">
         <v>10</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="2">
         <v>3</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E96" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="11">
         <v>96</v>
       </c>
-      <c r="B97">
+      <c r="B97" s="11">
         <v>21</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="11">
         <v>27</v>
       </c>
-      <c r="D97">
-        <v>1</v>
-      </c>
-      <c r="E97" t="s">
+      <c r="D97" s="2">
+        <v>1</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="11">
         <v>97</v>
       </c>
-      <c r="B98">
+      <c r="B98" s="11">
         <v>21</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="11">
         <v>40</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E98" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="11">
         <v>98</v>
       </c>
-      <c r="B99">
+      <c r="B99" s="11">
         <v>22</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="11">
         <v>41</v>
       </c>
-      <c r="D99">
-        <v>1</v>
-      </c>
-      <c r="E99" t="s">
+      <c r="D99" s="2">
+        <v>1</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="11">
         <v>99</v>
       </c>
-      <c r="B100">
+      <c r="B100" s="11">
         <v>22</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="11">
         <v>42</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E100" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="11">
         <v>100</v>
       </c>
-      <c r="B101">
+      <c r="B101" s="11">
         <v>22</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="11">
         <v>6</v>
       </c>
-      <c r="D101">
-        <v>1</v>
-      </c>
-      <c r="E101" t="s">
+      <c r="D101" s="2">
+        <v>1</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="11">
         <v>101</v>
       </c>
-      <c r="B102">
+      <c r="B102" s="11">
         <v>22</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="11">
         <v>32</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="11">
         <v>102</v>
       </c>
-      <c r="B103">
+      <c r="B103" s="11">
         <v>22</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="11">
         <v>28</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="2">
         <v>2</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="11">
         <v>103</v>
       </c>
-      <c r="B104">
+      <c r="B104" s="11">
         <v>22</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="11">
         <v>27</v>
       </c>
-      <c r="D104">
-        <v>1</v>
-      </c>
-      <c r="E104" t="s">
+      <c r="D104" s="2">
+        <v>1</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="11">
         <v>104</v>
       </c>
-      <c r="B105">
+      <c r="B105" s="11">
         <v>22</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="11">
         <v>43</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D105" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E105" s="2" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="11">
         <v>105</v>
       </c>
-      <c r="B106">
+      <c r="B106" s="11">
         <v>23</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="11">
         <v>10</v>
       </c>
-      <c r="D106">
-        <v>1</v>
-      </c>
-      <c r="E106" t="s">
+      <c r="D106" s="2">
+        <v>1</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="11">
         <v>106</v>
       </c>
-      <c r="B107">
+      <c r="B107" s="11">
         <v>23</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="11">
         <v>44</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="2">
         <v>2</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E107" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="11">
         <v>107</v>
       </c>
-      <c r="B108">
+      <c r="B108" s="11">
         <v>23</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="11">
         <v>37</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="2">
         <v>2</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E108" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="11">
         <v>108</v>
       </c>
-      <c r="B109">
+      <c r="B109" s="11">
         <v>23</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="11">
+        <v>53</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="11">
+        <v>109</v>
+      </c>
+      <c r="B110" s="11">
+        <v>23</v>
+      </c>
+      <c r="C110" s="11">
+        <v>48</v>
+      </c>
+      <c r="D110" s="2">
+        <v>1</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="11">
+        <v>110</v>
+      </c>
+      <c r="B111" s="11">
+        <v>23</v>
+      </c>
+      <c r="C111" s="11">
         <v>28</v>
       </c>
-      <c r="D109">
+      <c r="D111" s="2">
+        <v>1</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="11">
+        <v>111</v>
+      </c>
+      <c r="B112" s="11">
+        <v>23</v>
+      </c>
+      <c r="C112" s="11">
+        <v>9</v>
+      </c>
+      <c r="D112" s="2">
+        <v>1</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="11">
+        <v>112</v>
+      </c>
+      <c r="B113" s="11">
+        <v>23</v>
+      </c>
+      <c r="C113" s="11">
+        <v>45</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="11">
+        <v>113</v>
+      </c>
+      <c r="B114" s="11">
+        <v>23</v>
+      </c>
+      <c r="C114" s="11">
+        <v>46</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="11">
+        <v>114</v>
+      </c>
+      <c r="B115" s="11">
+        <v>23</v>
+      </c>
+      <c r="C115" s="11">
+        <v>27</v>
+      </c>
+      <c r="D115" s="2">
+        <v>1</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="11">
+        <v>115</v>
+      </c>
+      <c r="B116" s="11">
+        <v>23</v>
+      </c>
+      <c r="C116" s="11">
+        <v>28</v>
+      </c>
+      <c r="D116" s="2">
+        <v>1</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="11">
+        <v>116</v>
+      </c>
+      <c r="B117" s="11">
+        <v>24</v>
+      </c>
+      <c r="C117" s="11">
+        <v>10</v>
+      </c>
+      <c r="D117" s="2">
+        <v>1</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="11">
+        <v>117</v>
+      </c>
+      <c r="B118" s="11">
+        <v>24</v>
+      </c>
+      <c r="C118" s="11">
+        <v>47</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="11">
+        <v>118</v>
+      </c>
+      <c r="B119" s="11">
+        <v>24</v>
+      </c>
+      <c r="C119" s="11">
+        <v>48</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="11">
+        <v>119</v>
+      </c>
+      <c r="B120" s="11">
+        <v>24</v>
+      </c>
+      <c r="C120" s="11">
+        <v>49</v>
+      </c>
+      <c r="D120" s="2">
+        <v>1</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="11">
+        <v>120</v>
+      </c>
+      <c r="B121" s="11">
+        <v>24</v>
+      </c>
+      <c r="C121" s="11">
+        <v>50</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="11">
+        <v>121</v>
+      </c>
+      <c r="B122" s="11">
+        <v>24</v>
+      </c>
+      <c r="C122" s="11">
+        <v>46</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="11">
+        <v>122</v>
+      </c>
+      <c r="B123" s="11">
+        <v>24</v>
+      </c>
+      <c r="C123" s="11">
+        <v>51</v>
+      </c>
+      <c r="D123" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="11">
+        <v>123</v>
+      </c>
+      <c r="B124" s="11">
+        <v>24</v>
+      </c>
+      <c r="C124" s="11">
+        <v>34</v>
+      </c>
+      <c r="D124" s="2">
+        <v>1</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="11">
+        <v>124</v>
+      </c>
+      <c r="B125" s="11">
+        <v>24</v>
+      </c>
+      <c r="C125" s="11">
+        <v>47</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="11">
+        <v>125</v>
+      </c>
+      <c r="B126" s="11">
+        <v>24</v>
+      </c>
+      <c r="C126" s="11">
+        <v>52</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="11">
+        <v>126</v>
+      </c>
+      <c r="B127" s="11">
+        <v>24</v>
+      </c>
+      <c r="C127" s="11">
+        <v>49</v>
+      </c>
+      <c r="D127" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="11">
+        <v>127</v>
+      </c>
+      <c r="B128" s="11">
+        <v>24</v>
+      </c>
+      <c r="C128" s="11">
+        <v>24</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="11">
+        <v>24100621204701</v>
+      </c>
+      <c r="B129" s="11">
+        <v>241006212047</v>
+      </c>
+      <c r="C129" s="11">
+        <v>24100621204701</v>
+      </c>
+      <c r="D129" s="2">
+        <v>1</v>
+      </c>
+      <c r="E129" s="2">
         <v>2</v>
       </c>
-      <c r="E109" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110">
-        <v>109</v>
-      </c>
-      <c r="B110">
-        <v>23</v>
-      </c>
-      <c r="C110">
-        <v>45</v>
-      </c>
-      <c r="D110" t="s">
-        <v>98</v>
-      </c>
-      <c r="E110" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111">
-        <v>110</v>
-      </c>
-      <c r="B111">
-        <v>23</v>
-      </c>
-      <c r="C111">
-        <v>9</v>
-      </c>
-      <c r="D111" t="s">
-        <v>98</v>
-      </c>
-      <c r="E111" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112">
-        <v>111</v>
-      </c>
-      <c r="B112">
-        <v>23</v>
-      </c>
-      <c r="C112">
-        <v>46</v>
-      </c>
-      <c r="D112" t="s">
-        <v>98</v>
-      </c>
-      <c r="E112" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113">
-        <v>112</v>
-      </c>
-      <c r="B113">
-        <v>23</v>
-      </c>
-      <c r="C113">
-        <v>27</v>
-      </c>
-      <c r="D113">
-        <v>1</v>
-      </c>
-      <c r="E113" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114">
-        <v>113</v>
-      </c>
-      <c r="B114">
-        <v>23</v>
-      </c>
-      <c r="C114">
-        <v>28</v>
-      </c>
-      <c r="D114">
-        <v>1</v>
-      </c>
-      <c r="E114" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115">
-        <v>114</v>
-      </c>
-      <c r="B115">
-        <v>24</v>
-      </c>
-      <c r="C115">
-        <v>10</v>
-      </c>
-      <c r="D115">
-        <v>1</v>
-      </c>
-      <c r="E115" t="s">
-        <v>12</v>
-      </c>
-      <c r="F115" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116">
-        <v>115</v>
-      </c>
-      <c r="B116">
-        <v>24</v>
-      </c>
-      <c r="C116">
-        <v>47</v>
-      </c>
-      <c r="D116" t="s">
-        <v>98</v>
-      </c>
-      <c r="E116" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117">
-        <v>116</v>
-      </c>
-      <c r="B117">
-        <v>24</v>
-      </c>
-      <c r="C117">
-        <v>48</v>
-      </c>
-      <c r="D117" t="s">
-        <v>98</v>
-      </c>
-      <c r="E117" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118">
-        <v>117</v>
-      </c>
-      <c r="B118">
-        <v>24</v>
-      </c>
-      <c r="C118">
-        <v>49</v>
-      </c>
-      <c r="D118">
-        <v>1</v>
-      </c>
-      <c r="E118" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119">
-        <v>118</v>
-      </c>
-      <c r="B119">
-        <v>24</v>
-      </c>
-      <c r="C119">
-        <v>50</v>
-      </c>
-      <c r="D119" t="s">
-        <v>98</v>
-      </c>
-      <c r="E119" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120">
-        <v>119</v>
-      </c>
-      <c r="B120">
-        <v>24</v>
-      </c>
-      <c r="C120">
-        <v>46</v>
-      </c>
-      <c r="D120" t="s">
-        <v>98</v>
-      </c>
-      <c r="E120" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121">
-        <v>120</v>
-      </c>
-      <c r="B121">
-        <v>24</v>
-      </c>
-      <c r="C121">
-        <v>51</v>
-      </c>
-      <c r="D121">
-        <v>0.5</v>
-      </c>
-      <c r="E121" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122">
-        <v>121</v>
-      </c>
-      <c r="B122">
-        <v>24</v>
-      </c>
-      <c r="C122">
-        <v>34</v>
-      </c>
-      <c r="D122">
-        <v>1</v>
-      </c>
-      <c r="E122" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123">
-        <v>122</v>
-      </c>
-      <c r="B123">
-        <v>24</v>
-      </c>
-      <c r="C123">
-        <v>47</v>
-      </c>
-      <c r="D123" t="s">
-        <v>98</v>
-      </c>
-      <c r="E123" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124">
-        <v>123</v>
-      </c>
-      <c r="B124">
-        <v>24</v>
-      </c>
-      <c r="C124">
-        <v>52</v>
-      </c>
-      <c r="D124" t="s">
-        <v>98</v>
-      </c>
-      <c r="E124" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125">
-        <v>124</v>
-      </c>
-      <c r="B125">
-        <v>24</v>
-      </c>
-      <c r="C125">
-        <v>49</v>
-      </c>
-      <c r="D125">
-        <v>0.5</v>
-      </c>
-      <c r="E125" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126">
-        <v>125</v>
-      </c>
-      <c r="B126">
-        <v>24</v>
-      </c>
-      <c r="C126">
-        <v>24</v>
-      </c>
-      <c r="D126" t="s">
-        <v>98</v>
-      </c>
-      <c r="E126" t="s">
-        <v>109</v>
+      <c r="F129" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="11">
+        <v>24100621204702</v>
+      </c>
+      <c r="B130" s="11">
+        <v>241006212047</v>
+      </c>
+      <c r="C130" s="11">
+        <v>24100621204702</v>
+      </c>
+      <c r="D130" s="2">
+        <v>2</v>
+      </c>
+      <c r="E130" s="2">
+        <v>3</v>
+      </c>
+      <c r="F130" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="11">
+        <v>24100621204703</v>
+      </c>
+      <c r="B131" s="11">
+        <v>241006212047</v>
+      </c>
+      <c r="C131" s="11">
+        <v>5</v>
+      </c>
+      <c r="D131" s="2">
+        <v>2</v>
+      </c>
+      <c r="E131" s="2">
+        <v>3</v>
+      </c>
+      <c r="F131" s="2">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
